--- a/data/raw/全球主要资本市场情况.xlsx
+++ b/data/raw/全球主要资本市场情况.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="全球主要资本市场情况" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -427,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -470,13 +470,13 @@
         <v>NYSE全部股票</v>
       </c>
       <c r="B2" s="4">
-        <v>3390948.5119659677</v>
+        <v>3390943.9178413944</v>
       </c>
       <c r="C2" s="5">
-        <v>22182.719204755664</v>
+        <v>22182.68084329437</v>
       </c>
       <c r="D2" s="4">
-        <v>1.326960483067824</v>
+        <v>1.327169968040342</v>
       </c>
       <c r="E2" s="4">
         <v>15.592811584472656</v>
@@ -487,7 +487,7 @@
         <v>NASDAQ 精选市场(GS)</v>
       </c>
       <c r="B3" s="4">
-        <v>3174633.4732409124</v>
+        <v>3174633.477098567</v>
       </c>
       <c r="C3" s="5">
         <v>30557.65556412234</v>
@@ -507,10 +507,10 @@
         <v>763402.4138048369</v>
       </c>
       <c r="C4" s="5">
-        <v>12162.742713688189</v>
+        <v>12162.088238925991</v>
       </c>
       <c r="D4" s="4">
-        <v>3.082407628955444</v>
+        <v>3.083141569732459</v>
       </c>
       <c r="E4" s="4">
         <v>22.147794723510742</v>
@@ -521,13 +521,13 @@
         <v>港股主板</v>
       </c>
       <c r="B5" s="4">
-        <v>683846.3588581923</v>
+        <v>683847.5037441731</v>
       </c>
       <c r="C5" s="5">
         <v>1984.058436851112</v>
       </c>
       <c r="D5" s="4">
-        <v>0.486950827141131</v>
+        <v>0.486950681916333</v>
       </c>
       <c r="E5" s="4">
         <v>4.372848272323608</v>
@@ -535,284 +535,301 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="str">
-        <v>LSE主板</v>
+        <v>东证主要市场</v>
       </c>
       <c r="B6" s="4">
-        <v>499663.47687318455</v>
+        <v>566486.2778511815</v>
       </c>
       <c r="C6" s="5">
-        <v>1309.6104630015434</v>
+        <v>3699.032411716191</v>
       </c>
       <c r="D6" s="4">
-        <v>0.570461460904985</v>
+        <v>0.604110248370838</v>
       </c>
       <c r="E6" s="4">
-        <v>8.624422550201416</v>
+        <v>14.95246410369873</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="str">
-        <v>深证A股</v>
+        <v>LSE主板</v>
       </c>
       <c r="B7" s="4">
-        <v>494375.99342137406</v>
+        <v>499663.47687318455</v>
       </c>
       <c r="C7" s="5">
-        <v>15342.931912436756</v>
+        <v>1309.6104630015434</v>
       </c>
       <c r="D7" s="4">
-        <v>4.559475978766467</v>
+        <v>0.570461460904985</v>
       </c>
       <c r="E7" s="4">
-        <v>26.929828643798828</v>
+        <v>8.624422550201416</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="str">
-        <v>上市台股</v>
+        <v>深证A股</v>
       </c>
       <c r="B8" s="4">
-        <v>330565.53320540127</v>
+        <v>494375.99342137406</v>
       </c>
       <c r="C8" s="5">
-        <v>1998.555736005846</v>
+        <v>15342.931912436756</v>
       </c>
       <c r="D8" s="4">
-        <v>1.43650812090551</v>
+        <v>4.559475978766467</v>
       </c>
       <c r="E8" s="4">
-        <v>16.155561447143555</v>
+        <v>26.929828643798828</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="str">
-        <v>韩国主板市场</v>
+        <v>上市台股</v>
       </c>
       <c r="B9" s="4">
-        <v>294138.20427548065</v>
+        <v>330565.53320540127</v>
       </c>
       <c r="C9" s="5">
-        <v>1513.491209539325</v>
+        <v>1998.555736005846</v>
       </c>
       <c r="D9" s="4">
-        <v>1.461472047860231</v>
+        <v>1.43650812090551</v>
       </c>
       <c r="E9" s="4">
-        <v>6.032150268554688</v>
+        <v>16.155561447143555</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="str">
-        <v>创业板</v>
+        <v>韩国主板市场</v>
       </c>
       <c r="B10" s="4">
-        <v>218936.6155534309</v>
+        <v>294138.20427548065</v>
       </c>
       <c r="C10" s="5">
-        <v>7226.781310559082</v>
+        <v>1513.491209539325</v>
       </c>
       <c r="D10" s="4">
-        <v>5.198190598184782</v>
+        <v>1.461472047860231</v>
       </c>
       <c r="E10" s="4">
-        <v>36.030723571777344</v>
+        <v>6.032150268554688</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="str">
-        <v>科创板</v>
+        <v>创业板</v>
       </c>
       <c r="B11" s="4">
-        <v>168155.3060031891</v>
+        <v>218936.6155534309</v>
       </c>
       <c r="C11" s="5">
-        <v>3523.6656615895718</v>
+        <v>7226.781310559082</v>
       </c>
       <c r="D11" s="4">
-        <v>3.730986951329409</v>
+        <v>5.198190598184782</v>
       </c>
       <c r="E11" s="4">
-        <v>46.13898277282715</v>
+        <v>36.030723571777344</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="str">
-        <v>NASDAQ 全球市场(GM)</v>
+        <v>科创板</v>
       </c>
       <c r="B12" s="4">
-        <v>48343.58775506241</v>
+        <v>168155.3060031891</v>
       </c>
       <c r="C12" s="5">
-        <v>862.1706076814773</v>
+        <v>3523.6656615895718</v>
       </c>
       <c r="D12" s="4">
-        <v>1.613718561554944</v>
+        <v>3.730986951329409</v>
       </c>
       <c r="E12" s="4">
-        <v>-1.044248938560486</v>
+        <v>46.13898277282715</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="str">
-        <v>上柜台股</v>
+        <v>NASDAQ 全球市场(GM)</v>
       </c>
       <c r="B13" s="4">
-        <v>24283.421975476263</v>
+        <v>48343.58775506241</v>
       </c>
       <c r="C13" s="5">
-        <v>495.8840498282428</v>
+        <v>862.1706076814773</v>
       </c>
       <c r="D13" s="4">
-        <v/>
+        <v>1.613718561554944</v>
       </c>
       <c r="E13" s="4">
-        <v>16.22178077697754</v>
+        <v>-1.044248938560486</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="str">
-        <v>韩国创业板市场</v>
+        <v>上柜台股</v>
       </c>
       <c r="B14" s="4">
-        <v>21982.057049874496</v>
+        <v>24283.421975476263</v>
       </c>
       <c r="C14" s="5">
-        <v>625.5732497519655</v>
+        <v>495.8840498282428</v>
       </c>
       <c r="D14" s="4">
-        <v>5.832074809467317</v>
+        <v/>
       </c>
       <c r="E14" s="4">
-        <v>4.165733814239502</v>
+        <v>16.22178077697754</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="str">
-        <v>东证标准市场</v>
+        <v>韩国创业板市场</v>
       </c>
       <c r="B15" s="4">
-        <v>13726.700022004132</v>
+        <v>21982.057049874496</v>
       </c>
       <c r="C15" s="5">
-        <v>98.06809531419188</v>
+        <v>625.5732497519655</v>
       </c>
       <c r="D15" s="4">
-        <v>0.610983336837163</v>
+        <v>5.832074809467317</v>
       </c>
       <c r="E15" s="4">
-        <v>11.085108280181885</v>
+        <v>4.165733814239502</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="str">
-        <v>AMEX全部股票</v>
+        <v>东证标准市场</v>
       </c>
       <c r="B16" s="4">
-        <v>10486.641211235157</v>
+        <v>13726.700022004132</v>
       </c>
       <c r="C16" s="5">
-        <v>156.23212179115174</v>
+        <v>98.06809531419188</v>
       </c>
       <c r="D16" s="4">
-        <v>8.11702259104102</v>
+        <v>0.610983336837163</v>
       </c>
       <c r="E16" s="4">
-        <v>-1.554812431335449</v>
+        <v>11.085108280181885</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="str">
-        <v>北证A股</v>
+        <v>AMEX全部股票</v>
       </c>
       <c r="B17" s="4">
-        <v>8475.922990335204</v>
+        <v>10486.641211235157</v>
       </c>
       <c r="C17" s="5">
-        <v>277.0971314301894</v>
+        <v>156.23212179115174</v>
       </c>
       <c r="D17" s="4">
-        <v>5.537595874137328</v>
+        <v>8.11702259104102</v>
       </c>
       <c r="E17" s="4">
-        <v>30.43874740600586</v>
+        <v>-1.554812431335449</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="str">
-        <v>LSE创业板(AIM)</v>
+        <v>北证A股</v>
       </c>
       <c r="B18" s="4">
-        <v>6918.691711975117</v>
+        <v>8475.922990335204</v>
       </c>
       <c r="C18" s="5">
-        <v>23.334342381650973</v>
+        <v>277.0971314301894</v>
       </c>
       <c r="D18" s="4">
-        <v>0.884970997699793</v>
+        <v>5.537595874137328</v>
       </c>
       <c r="E18" s="4">
-        <v>-0.882110118865967</v>
+        <v>30.43874740600586</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="str">
-        <v>东证增长市场</v>
+        <v>LSE创业板(AIM)</v>
       </c>
       <c r="B19" s="4">
-        <v>3637.5515898201293</v>
+        <v>6918.691711975117</v>
       </c>
       <c r="C19" s="5">
-        <v>87.52077208983353</v>
+        <v>23.33427797955002</v>
       </c>
       <c r="D19" s="4">
-        <v>1.436487877744203</v>
+        <v>0.885020548344512</v>
       </c>
       <c r="E19" s="4">
-        <v>12.532909393310547</v>
+        <v>-0.882110118865967</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="str">
-        <v>新加坡创业板</v>
+        <v>东证增长市场</v>
       </c>
       <c r="B20" s="4">
-        <v>800.933194216071</v>
+        <v>3637.5515898201293</v>
       </c>
       <c r="C20" s="5">
-        <v>2.361682858526854</v>
+        <v>87.52077208983353</v>
       </c>
       <c r="D20" s="4">
-        <v>0.26288095030168</v>
+        <v>1.436487877744203</v>
       </c>
       <c r="E20" s="4">
-        <v>-1.082257986068726</v>
+        <v>12.532909393310547</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="str">
+        <v>新加坡创业板</v>
+      </c>
+      <c r="B21" s="4">
+        <v>800.933194216071</v>
+      </c>
+      <c r="C21" s="5">
+        <v>2.361682858526854</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.26288095030168</v>
+      </c>
+      <c r="E21" s="4">
+        <v>-1.082257986068726</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="str">
         <v>港股创业板</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B22" s="4">
         <v>712.1603933357102</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C22" s="5">
         <v>1.210327669130699</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D22" s="4">
         <v>0.215937272638097</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E22" s="4">
         <v>-1.855664014816284</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="str">
+    <row r="24">
+      <c r="A24" s="6" t="str">
         <v>数据来源：Wind</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
   </ignoredErrors>
 </worksheet>
 </file>